--- a/Total_Oxide_Calculations/Oxides_SILLS.xlsx
+++ b/Total_Oxide_Calculations/Oxides_SILLS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unibe365-my.sharepoint.com/personal/sebastian_stumpf_unibe_ch/Documents/PhD/ICP-Base/ICP-Base_dev/Total_Oxide_Calculations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="11_C93881D2F499C0CA9E24614525B7E03D54DD654E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0BDF1FB-4643-4DA0-869D-F0583EB1AAA0}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="11_C93881D2F499C0CA9E24614525B7E03D54DD654E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D73023AC-4EE8-492D-AE2F-838435488041}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="29">
   <si>
     <t>SiO2</t>
   </si>
@@ -51,9 +51,6 @@
     <t>Ca</t>
   </si>
   <si>
-    <t>Cr</t>
-  </si>
-  <si>
     <t>Fe</t>
   </si>
   <si>
@@ -81,9 +78,6 @@
     <t>Ti</t>
   </si>
   <si>
-    <t>Cr2O3</t>
-  </si>
-  <si>
     <t>P2O5</t>
   </si>
   <si>
@@ -108,28 +102,7 @@
     <t>Ca43</t>
   </si>
   <si>
-    <t>Si29</t>
-  </si>
-  <si>
-    <t>Mg25</t>
-  </si>
-  <si>
-    <t>K39</t>
-  </si>
-  <si>
     <t>Al27</t>
-  </si>
-  <si>
-    <t>Na23</t>
-  </si>
-  <si>
-    <t>Ti49</t>
-  </si>
-  <si>
-    <t>Fe57</t>
-  </si>
-  <si>
-    <t>Cr53</t>
   </si>
   <si>
     <t>Major_Element</t>
@@ -479,11 +452,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -491,19 +464,19 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -517,10 +490,10 @@
         <v>1.8895</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -536,178 +509,170 @@
         <v>1.3992</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C4" s="1">
-        <v>1.4616</v>
-      </c>
-      <c r="D4" t="s">
-        <v>34</v>
+        <v>2.1393</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2">
-        <v>1.2865</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
+        <v>18</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1.6679999999999999</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C6" s="1">
-        <v>1.2045999999999999</v>
-      </c>
-      <c r="D6" t="s">
-        <v>29</v>
+        <v>1.8895</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="1">
-        <v>1.6583000000000001</v>
-      </c>
-      <c r="D7" t="s">
-        <v>28</v>
+        <v>5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1.2865</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C8" s="2">
         <v>1.2911999999999999</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="4">
-        <v>1.3480000000000001</v>
-      </c>
-      <c r="D9" t="s">
-        <v>31</v>
+        <v>11</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1.6583000000000001</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C10" s="1">
-        <v>2.2913999999999999</v>
+        <v>1.3992</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="1">
-        <v>2.1393</v>
-      </c>
-      <c r="D11" t="s">
-        <v>27</v>
+        <v>2</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1.3480000000000001</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1.2045999999999999</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="4">
-        <v>1.6679999999999999</v>
-      </c>
-      <c r="D12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
+      <c r="C13" s="1">
+        <v>2.2913999999999999</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F14" s="3"/>
@@ -741,9 +706,6 @@
     </row>
     <row r="24" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F24" s="3"/>
-    </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F25" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
